--- a/artfynd/A 45032-2023 artfynd.xlsx
+++ b/artfynd/A 45032-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45032-2023 artfynd.xlsx
+++ b/artfynd/A 45032-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>110047843</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601386.9143398623</v>
+        <v>601387</v>
       </c>
       <c r="R2" t="n">
-        <v>7305787.43850216</v>
+        <v>7305788</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>110047872</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601383.8469790473</v>
+        <v>601384</v>
       </c>
       <c r="R3" t="n">
-        <v>7305804.543110694</v>
+        <v>7305804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 45032-2023 artfynd.xlsx
+++ b/artfynd/A 45032-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110047843</v>
+        <v>134763644</v>
       </c>
       <c r="B2" t="n">
-        <v>83173</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nya Bergnäs, Pi lm</t>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601387</v>
+        <v>601484</v>
       </c>
       <c r="R2" t="n">
-        <v>7305788</v>
+        <v>7306057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,61 +756,66 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog med hög medelålder</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110047872</v>
+        <v>134763645</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>78393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nya Bergnäs, Pi lm</t>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601384</v>
+        <v>601351</v>
       </c>
       <c r="R3" t="n">
-        <v>7305804</v>
+        <v>7305865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,19 +858,728 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog med hög medelålder</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134763649</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>864</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601505</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7306047</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Stamtät, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134763648</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601495</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7306037</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Stamtät, lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134763640</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601437</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7305701</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog med hög medelålder</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110047843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nya Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7305788</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Jonas Nordenström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134763639</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601379</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7305864</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog med hög medelålder</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134763641</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601425</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7305851</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Luckig, lövrik grannaturskog med hög medelålder</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110047872</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nya Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601384</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7305804</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45032-2023 artfynd.xlsx
+++ b/artfynd/A 45032-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763644</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763645</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763648</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763640</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763639</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763641</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,8 +1625,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>